--- a/data/trans_orig/P04A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023</t>
+          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37410</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>37911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65661</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47569</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68363</t>
+          <t>70421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104299</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146811</t>
+          <t>145176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>92551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120514</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205817</t>
+          <t>204969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255619</t>
+          <t>259302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111091</t>
+          <t>111571</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152397</t>
+          <t>152425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123402</t>
+          <t>125823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>153219</t>
+          <t>154479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>246310</t>
+          <t>242776</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296317</t>
+          <t>298102</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>28786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77395</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>83298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125710</t>
+          <t>129203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>37036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76392</t>
+          <t>75418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121338</t>
+          <t>120617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148067</t>
+          <t>146775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207332</t>
+          <t>204179</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143608</t>
+          <t>143108</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>182913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>308573</t>
+          <t>306514</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>380984</t>
+          <t>374429</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193730</t>
+          <t>190393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>248194</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224330</t>
+          <t>224725</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265135</t>
+          <t>266264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425049</t>
+          <t>427967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>497824</t>
+          <t>498616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>54756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>37799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60695</t>
+          <t>63049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106094</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68567</t>
+          <t>67399</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>63115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96594</t>
+          <t>92943</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90993</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>121823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162042</t>
+          <t>161428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206774</t>
+          <t>204844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142577</t>
+          <t>143320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180148</t>
+          <t>178833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143881</t>
+          <t>143013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174583</t>
+          <t>174478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296450</t>
+          <t>296474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>341556</t>
+          <t>344042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36707</t>
+          <t>36575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25362</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60173</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43943</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>252492</t>
+          <t>254268</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>83235</t>
+          <t>84569</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>319005</t>
+          <t>326941</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>19875</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30878</t>
+          <t>30551</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60883</t>
+          <t>62325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101728</t>
+          <t>102155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>57156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115786</t>
+          <t>115802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>122690</t>
+          <t>120237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>204531</t>
+          <t>202513</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138843</t>
+          <t>138396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>181008</t>
+          <t>180135</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150700</t>
+          <t>152428</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>307168</t>
+          <t>306077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>298260</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>465961</t>
+          <t>469110</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>318</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>147353</t>
+          <t>150979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>181652</t>
+          <t>163086</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20836</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29996</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>144527</t>
+          <t>143454</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>160489</t>
+          <t>160753</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>104594</t>
+          <t>100984</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>234506</t>
+          <t>234950</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>234001</t>
+          <t>250062</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>388940</t>
+          <t>387596</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,62 +4740,62 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>6240</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>36409</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>29223</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>42649</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>68316</t>
+          <t>67236</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>57565</t>
+          <t>58134</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>87718</t>
+          <t>85327</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>119437</t>
+          <t>119664</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>141254</t>
+          <t>142113</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>170490</t>
+          <t>171523</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156435</t>
+          <t>156428</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>181529</t>
+          <t>180868</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>306555</t>
+          <t>305464</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>342487</t>
+          <t>346234</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,82 +5628,82 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>7132</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>13723</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>14319</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>23232</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>7132</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>13477</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>14319</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>7256</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>22499</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>56269</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>105607</t>
+          <t>105749</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>36193</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>110653</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>97101</t>
+          <t>94897</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>194134</t>
+          <t>188658</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>31164</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>119683</t>
+          <t>119430</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>165475</t>
+          <t>167736</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>77188</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>206639</t>
+          <t>206714</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>184111</t>
+          <t>168285</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>350403</t>
+          <t>353783</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>337026</t>
+          <t>337276</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>394145</t>
+          <t>394919</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>496212</t>
+          <t>496214</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>725184</t>
+          <t>715983</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>860199</t>
+          <t>859574</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1146428</t>
+          <t>1171863</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>105630</t>
+          <t>104749</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51713</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>84423</t>
+          <t>86289</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>83576</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>170801</t>
+          <t>170595</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>34028</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>64577</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>203139</t>
+          <t>204685</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>144194</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>184924</t>
+          <t>180913</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>182979</t>
+          <t>194097</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>366174</t>
+          <t>369565</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>581530</t>
+          <t>579850</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>816866</t>
+          <t>816884</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>442994</t>
+          <t>447847</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>490654</t>
+          <t>493976</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1056617</t>
+          <t>1052623</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1341372</t>
+          <t>1336656</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>79225</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>83883</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>267033</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>387848</t>
+          <t>392469</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>340228</t>
+          <t>339552</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>712779</t>
+          <t>692543</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>667054</t>
+          <t>661637</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>1046314</t>
+          <t>1017651</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>131457</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>206495</t>
+          <t>206914</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>107363</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>156850</t>
+          <t>159616</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>260405</t>
+          <t>256461</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>350632</t>
+          <t>346746</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>637886</t>
+          <t>637056</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>890894</t>
+          <t>899659</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>684918</t>
+          <t>651829</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>901030</t>
+          <t>906038</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1397476</t>
+          <t>1391446</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1771538</t>
+          <t>1756155</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1903297</t>
+          <t>1897379</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2344781</t>
+          <t>2328557</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2064087</t>
+          <t>2077064</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2481545</t>
+          <t>2508919</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>4002936</t>
+          <t>4027311</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4603104</t>
+          <t>4626237</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>551</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>551</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>52812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>48197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45949</t>
+          <t>85418</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64793</t>
+          <t>105154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31178</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>40677</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35831</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70421</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>124727</t>
+          <t>116178</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104601</t>
+          <t>99542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>105669</t>
+          <t>119864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92551</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>230396</t>
+          <t>236042</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204969</t>
+          <t>214554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259302</t>
+          <t>261362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131121</t>
+          <t>125444</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>108086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152425</t>
+          <t>144867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>139742</t>
+          <t>141402</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125823</t>
+          <t>127266</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154479</t>
+          <t>156052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>270863</t>
+          <t>266846</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>242776</t>
+          <t>244016</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>298102</t>
+          <t>289725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28786</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34380</t>
+          <t>33516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27667</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55995</t>
+          <t>69235</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39884</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76153</t>
+          <t>88695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62314</t>
+          <t>78213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102983</t>
+          <t>131490</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83298</t>
+          <t>109170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129203</t>
+          <t>159772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48950</t>
+          <t>46655</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>31034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47109</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37036</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62018</t>
+          <t>60272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>96059</t>
+          <t>94405</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75418</t>
+          <t>74712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120617</t>
+          <t>117069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>175565</t>
+          <t>173635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146775</t>
+          <t>149366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>205336</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>163399</t>
+          <t>166702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143108</t>
+          <t>146814</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182913</t>
+          <t>185821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>338964</t>
+          <t>340336</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>306514</t>
+          <t>308602</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>374429</t>
+          <t>376749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>218896</t>
+          <t>223092</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>190393</t>
+          <t>197460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>251420</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>244996</t>
+          <t>256054</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224725</t>
+          <t>235777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>266264</t>
+          <t>279664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>479146</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427967</t>
+          <t>443187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>498616</t>
+          <t>511882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>517001</t>
+          <t>529308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>517001</t>
+          <t>529308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517001</t>
+          <t>529308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>513677</t>
+          <t>545201</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513677</t>
+          <t>545201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513677</t>
+          <t>545201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1030678</t>
+          <t>1074509</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030678</t>
+          <t>1074509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1030678</t>
+          <t>1074509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40589</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>59545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63049</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>88652</t>
+          <t>97424</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>80266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106104</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>24323</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41058</t>
+          <t>42076</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>78164</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63115</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92943</t>
+          <t>93875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>104893</t>
+          <t>108516</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91036</t>
+          <t>93832</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121823</t>
+          <t>123790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>183057</t>
+          <t>187577</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161428</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204844</t>
+          <t>210390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>160736</t>
+          <t>155714</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143320</t>
+          <t>138943</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178833</t>
+          <t>173529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>158851</t>
+          <t>158364</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143013</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174478</t>
+          <t>173898</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>319588</t>
+          <t>314078</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296474</t>
+          <t>291993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>344042</t>
+          <t>337666</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>355117</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>355117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>355117</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>663914</t>
+          <t>671111</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>663914</t>
+          <t>671111</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>663914</t>
+          <t>671111</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>33596</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>589</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,22 +3293,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>70665</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56514</t>
+          <t>94685</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>112449</t>
+          <t>61268</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>254268</t>
+          <t>79335</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>152586</t>
+          <t>131932</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>84569</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>326941</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62325</t>
+          <t>64765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>109286</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>89296</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>81817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115802</t>
+          <t>116447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>169146</t>
+          <t>185691</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>120237</t>
+          <t>161038</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>202513</t>
+          <t>214542</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>160487</t>
+          <t>180209</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180135</t>
+          <t>205671</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>249836</t>
+          <t>235042</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152428</t>
+          <t>215165</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>306077</t>
+          <t>255269</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>410322</t>
+          <t>415252</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>298260</t>
+          <t>383762</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>469110</t>
+          <t>450158</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>300816</t>
+          <t>363004</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>300816</t>
+          <t>363004</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>300816</t>
+          <t>363004</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>475557</t>
+          <t>421394</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>475557</t>
+          <t>421394</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>475557</t>
+          <t>421394</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>776372</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>776372</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>776372</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>399</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4018,102 +4018,102 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2766</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2166</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>10697</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>2325</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>1839</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>4761</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>150979</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>65838</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>163086</t>
+          <t>41638</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>32773</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>153227</t>
+          <t>165558</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>143454</t>
+          <t>154192</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>160753</t>
+          <t>174933</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>188284</t>
+          <t>201050</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>100984</t>
+          <t>191974</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>234950</t>
+          <t>207962</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>341512</t>
+          <t>366608</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>250062</t>
+          <t>351863</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>387596</t>
+          <t>378423</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>178069</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>258367</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>258367</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>258367</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>436436</t>
+          <t>433404</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>436436</t>
+          <t>433404</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>436436</t>
+          <t>433404</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>39405</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>27241</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>38514</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>42950</t>
+          <t>51667</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>37267</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>42649</t>
+          <t>43021</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67236</t>
+          <t>67153</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>36040</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>58134</t>
+          <t>57863</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>101884</t>
+          <t>100878</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>85327</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>119664</t>
+          <t>118234</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>156787</t>
+          <t>153685</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>142113</t>
+          <t>139539</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>171523</t>
+          <t>169195</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>169460</t>
+          <t>172587</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156428</t>
+          <t>158558</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>180868</t>
+          <t>184564</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>326246</t>
+          <t>326272</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>305464</t>
+          <t>306495</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>346234</t>
+          <t>345672</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>27580</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>16854</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>56269</t>
+          <t>90406</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>105749</t>
+          <t>138785</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>123907</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>36193</t>
+          <t>104770</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>146411</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>151944</t>
+          <t>234870</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>94897</t>
+          <t>206999</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>188658</t>
+          <t>270830</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>21937</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>33867</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>23427</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>48197</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>141438</t>
+          <t>151662</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>119430</t>
+          <t>128874</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>167736</t>
+          <t>177246</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>150483</t>
+          <t>167617</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>77188</t>
+          <t>146557</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>206714</t>
+          <t>188451</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>291921</t>
+          <t>319279</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>168285</t>
+          <t>288730</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>353783</t>
+          <t>353156</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>367451</t>
+          <t>411531</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>337276</t>
+          <t>378506</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>394919</t>
+          <t>441170</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>587916</t>
+          <t>440877</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>496214</t>
+          <t>414128</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>715983</t>
+          <t>464887</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>955366</t>
+          <t>852408</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>859574</t>
+          <t>810340</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1171863</t>
+          <t>891129</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>614809</t>
+          <t>709965</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>614809</t>
+          <t>709965</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>614809</t>
+          <t>709965</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>840218</t>
+          <t>761273</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>840218</t>
+          <t>761273</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>840218</t>
+          <t>761273</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1455027</t>
+          <t>1471239</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1455027</t>
+          <t>1471239</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1455027</t>
+          <t>1471239</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>37857</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>71705</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>29923</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>104749</t>
+          <t>127100</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>68211</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>86289</t>
+          <t>103252</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>137263</t>
+          <t>190610</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>83576</t>
+          <t>162696</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>170595</t>
+          <t>218564</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>163683</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>64577</t>
+          <t>140337</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>204685</t>
+          <t>190404</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>162308</t>
+          <t>185075</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>165629</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>180913</t>
+          <t>208346</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>305637</t>
+          <t>348758</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>194097</t>
+          <t>317725</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>369565</t>
+          <t>383179</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>679326</t>
+          <t>489623</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>579850</t>
+          <t>458462</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>816884</t>
+          <t>516177</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>469459</t>
+          <t>536368</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>447847</t>
+          <t>510828</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>493976</t>
+          <t>562604</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>1148785</t>
+          <t>1025991</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1052623</t>
+          <t>985378</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1336656</t>
+          <t>1063892</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>927065</t>
+          <t>796228</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>927065</t>
+          <t>796228</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>927065</t>
+          <t>796228</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>716336</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>716336</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>716336</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1643401</t>
+          <t>1626032</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1643401</t>
+          <t>1626032</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1643401</t>
+          <t>1626032</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,102 +7085,102 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>19262</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>41562</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>67790</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>48737</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>92877</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>36674</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>55512</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>37965</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>78140</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7198,67 +7198,67 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>83436</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>55216</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>42578</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>70146</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>50149</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>37978</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>65679</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>106021</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>99346</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>142069</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>337144</t>
+          <t>498412</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>267033</t>
+          <t>448695</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>392469</t>
+          <t>547089</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>456126</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>339552</t>
+          <t>418028</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>692543</t>
+          <t>493718</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>788165</t>
+          <t>954538</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>661637</t>
+          <t>891772</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>1017651</t>
+          <t>1019000</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>128722</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>206914</t>
+          <t>192107</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>107086</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>159616</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>305322</t>
+          <t>300859</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>256461</t>
+          <t>265254</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>346746</t>
+          <t>335113</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>811412</t>
+          <t>840053</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>637056</t>
+          <t>782188</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>899659</t>
+          <t>900527</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>830589</t>
+          <t>901411</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>651829</t>
+          <t>852137</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>906038</t>
+          <t>947552</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>1642001</t>
+          <t>1741464</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1391446</t>
+          <t>1670810</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1756155</t>
+          <t>1818976</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2028030</t>
+          <t>1904856</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1897379</t>
+          <t>1839438</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2328557</t>
+          <t>1970047</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2208544</t>
+          <t>2141743</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2077064</t>
+          <t>2088751</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2508919</t>
+          <t>2197717</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>4236574</t>
+          <t>4046600</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>4027311</t>
+          <t>3961917</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4626237</t>
+          <t>4131355</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
